--- a/EXCEL/Exercise Files/Chapter02/02_06_RunningAverage.xlsx
+++ b/EXCEL/Exercise Files/Chapter02/02_06_RunningAverage.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25407"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Curtis\Desktop\Exercise Files\Chapter02\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\neha work\Data Analytics\EXCEL\Exercise Files\Chapter02\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08BC910D-D795-451B-804B-A1A8C0A05753}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{258EC77F-41FD-48A3-BF8C-7A7556312A96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="12549" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="179021"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -23,6 +23,10 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -88,8 +92,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -134,14 +138,15 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -424,16 +429,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.84375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.3828125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.23046875" customWidth="1"/>
-    <col min="4" max="4" width="16.15234375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.3828125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.21875" customWidth="1"/>
+    <col min="4" max="4" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -450,113 +455,197 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="2">
         <v>4969</v>
       </c>
-      <c r="C2" s="2"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C2" s="2">
+        <f>SUM($B$2:B2)</f>
+        <v>4969</v>
+      </c>
+      <c r="D2" s="3">
+        <f>AVERAGE($B$2:B2)</f>
+        <v>4969</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="2">
         <v>5705</v>
       </c>
-      <c r="C3" s="2"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C3" s="2">
+        <f>SUM($B$2:B3)</f>
+        <v>10674</v>
+      </c>
+      <c r="D3" s="3">
+        <f>AVERAGE($B$2:B3)</f>
+        <v>5337</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="2">
         <v>9721</v>
       </c>
-      <c r="C4" s="2"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C4" s="2">
+        <f>SUM($B$2:B4)</f>
+        <v>20395</v>
+      </c>
+      <c r="D4" s="3">
+        <f>AVERAGE($B$2:B4)</f>
+        <v>6798.333333333333</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="2">
         <v>6481</v>
       </c>
-      <c r="C5" s="2"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C5" s="2">
+        <f>SUM($B$2:B5)</f>
+        <v>26876</v>
+      </c>
+      <c r="D5" s="3">
+        <f>AVERAGE($B$2:B5)</f>
+        <v>6719</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="2">
         <v>5311</v>
       </c>
-      <c r="C6" s="2"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C6" s="2">
+        <f>SUM($B$2:B6)</f>
+        <v>32187</v>
+      </c>
+      <c r="D6" s="3">
+        <f>AVERAGE($B$2:B6)</f>
+        <v>6437.4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="2">
         <v>6987</v>
       </c>
-      <c r="C7" s="2"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C7" s="2">
+        <f>SUM($B$2:B7)</f>
+        <v>39174</v>
+      </c>
+      <c r="D7" s="3">
+        <f>AVERAGE($B$2:B7)</f>
+        <v>6529</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>10</v>
       </c>
       <c r="B8" s="2">
         <v>8435</v>
       </c>
-      <c r="C8" s="2"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C8" s="2">
+        <f>SUM($B$2:B8)</f>
+        <v>47609</v>
+      </c>
+      <c r="D8" s="3">
+        <f>AVERAGE($B$2:B8)</f>
+        <v>6801.2857142857147</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="2">
         <v>3443</v>
       </c>
-      <c r="C9" s="2"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C9" s="2">
+        <f>SUM($B$2:B9)</f>
+        <v>51052</v>
+      </c>
+      <c r="D9" s="3">
+        <f>AVERAGE($B$2:B9)</f>
+        <v>6381.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>12</v>
       </c>
       <c r="B10" s="2">
         <v>3859</v>
       </c>
-      <c r="C10" s="2"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C10" s="2">
+        <f>SUM($B$2:B10)</f>
+        <v>54911</v>
+      </c>
+      <c r="D10" s="3">
+        <f>AVERAGE($B$2:B10)</f>
+        <v>6101.2222222222226</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>13</v>
       </c>
       <c r="B11" s="2">
         <v>4835</v>
       </c>
-      <c r="C11" s="2"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C11" s="2">
+        <f>SUM($B$2:B11)</f>
+        <v>59746</v>
+      </c>
+      <c r="D11" s="3">
+        <f>AVERAGE($B$2:B11)</f>
+        <v>5974.6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>14</v>
       </c>
       <c r="B12" s="2">
         <v>9139</v>
       </c>
-      <c r="C12" s="2"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C12" s="2">
+        <f>SUM($B$2:B12)</f>
+        <v>68885</v>
+      </c>
+      <c r="D12" s="3">
+        <f>AVERAGE($B$2:B12)</f>
+        <v>6262.272727272727</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>15</v>
       </c>
       <c r="B13" s="2">
         <v>9928</v>
       </c>
-      <c r="C13" s="2"/>
+      <c r="C13" s="2">
+        <f>SUM($B$2:B13)</f>
+        <v>78813</v>
+      </c>
+      <c r="D13" s="3">
+        <f>AVERAGE($B$2:B13)</f>
+        <v>6567.75</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
